--- a/W/A2Pico2LiteW_BOM.xlsx
+++ b/W/A2Pico2LiteW_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2Pico2LiteW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951F461A-C906-42E1-B2AF-528CD8FA98CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3105FFC-15B1-4DCB-BDDA-20B69499570C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>Comment</t>
   </si>
@@ -115,18 +115,12 @@
     <t>C269104</t>
   </si>
   <si>
-    <t>2k</t>
-  </si>
-  <si>
     <t>D1,D2</t>
   </si>
   <si>
     <t>FU1</t>
   </si>
   <si>
-    <t>C4109</t>
-  </si>
-  <si>
     <t>20-pin female header 5mm PN1X20-B CVILUX CB34202V100</t>
   </si>
   <si>
@@ -157,7 +151,22 @@
     <t>C22046</t>
   </si>
   <si>
-    <t>R1,R3</t>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>20k</t>
+  </si>
+  <si>
+    <t>10k</t>
+  </si>
+  <si>
+    <t>C25744</t>
+  </si>
+  <si>
+    <t>C25545</t>
   </si>
 </sst>
 </file>
@@ -623,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="59.54296875" style="2" bestFit="1" customWidth="1"/>
@@ -648,10 +657,10 @@
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -665,7 +674,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>10</v>
@@ -679,7 +688,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>7</v>
@@ -690,14 +699,14 @@
     </row>
     <row r="5" spans="1:4" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="20" customHeight="1">
@@ -705,7 +714,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -716,30 +725,44 @@
     </row>
     <row r="7" spans="1:4" ht="20" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="20" customHeight="1">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="20" customHeight="1">
+      <c r="A9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>25</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/W/A2Pico2LiteW_BOM.xlsx
+++ b/W/A2Pico2LiteW_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2Pico2LiteW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3105FFC-15B1-4DCB-BDDA-20B69499570C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AE73A9-99A3-4EF7-81D1-A4000C587B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>Comment</t>
   </si>
@@ -136,9 +136,6 @@
     <t>C1,C2</t>
   </si>
   <si>
-    <t>R2</t>
-  </si>
-  <si>
     <t>U2</t>
   </si>
   <si>
@@ -151,22 +148,7 @@
     <t>C22046</t>
   </si>
   <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>20k</t>
-  </si>
-  <si>
-    <t>10k</t>
-  </si>
-  <si>
-    <t>C25744</t>
-  </si>
-  <si>
-    <t>C25545</t>
+    <t>R1,R2</t>
   </si>
 </sst>
 </file>
@@ -632,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="59.54296875" style="2" bestFit="1" customWidth="1"/>
@@ -714,7 +696,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -724,45 +706,17 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="20" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="20" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="A7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="20" customHeight="1">
-      <c r="A9" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>24</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
